--- a/dia-1/src/main/resources/static/files/sample.xlsx
+++ b/dia-1/src/main/resources/static/files/sample.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\dia-1\src\main\resources\static\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAHUL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062665B2-3509-4A3E-9640-75E58B40F054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15030" windowHeight="6075" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diamond" sheetId="1" r:id="rId1"/>
@@ -2092,7 +2093,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -2489,11 +2490,11 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3009,21 +3010,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table1219" displayName="Table1219" ref="A1:M21" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1219" displayName="Table1219" ref="A1:M21" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <tableColumns count="13">
-    <tableColumn id="11" name="ID" dataDxfId="12"/>
-    <tableColumn id="1" name="Design No" dataDxfId="11"/>
-    <tableColumn id="12" name="Order Id" dataDxfId="10"/>
-    <tableColumn id="2" name="Item" dataDxfId="9"/>
-    <tableColumn id="3" name="Gross" dataDxfId="8"/>
-    <tableColumn id="4" name="Net" dataDxfId="7"/>
-    <tableColumn id="5" name="Vilandi Ct" dataDxfId="6"/>
-    <tableColumn id="6" name="Diamonds Ct" dataDxfId="5"/>
-    <tableColumn id="7" name="Beads Ct" dataDxfId="4"/>
-    <tableColumn id="8" name="Pearls Gm " dataDxfId="3"/>
-    <tableColumn id="14" name="SS Pearls" dataDxfId="2"/>
-    <tableColumn id="9" name="Other St  Ct" dataDxfId="1"/>
-    <tableColumn id="10" name="Remarks" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="ID" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Design No" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Order Id" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Item" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Gross" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Net" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Vilandi Ct" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Diamonds Ct" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Beads Ct" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Pearls Gm " dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="SS Pearls" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Other St  Ct" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3291,21 +3292,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N81"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="5" width="21.85546875" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="2" max="3" width="13.81640625" customWidth="1"/>
+    <col min="4" max="5" width="21.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
     <col min="10" max="10" width="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="18.85546875" customWidth="1"/>
-    <col min="13" max="13" width="33.28515625" customWidth="1"/>
+    <col min="11" max="12" width="18.81640625" customWidth="1"/>
+    <col min="13" max="13" width="33.26953125" customWidth="1"/>
     <col min="14" max="14" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17.25">
+    <row r="1" spans="1:14" ht="17">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -6550,25 +6551,30 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576" xr:uid="{C67605F5-B6AB-4B38-BADA-C0611668B589}">
+      <formula1>"Diamond Rings,Diamond Earrings,Diamond Bangles / Bracelets,Diamond Pendants / Pendant Sets,Diamond Halfsets"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="3" width="29.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="2" max="3" width="29.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.42578125" customWidth="1"/>
+    <col min="15" max="15" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" customWidth="1"/>
     <col min="18" max="18" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30">
+    <row r="1" spans="1:18" ht="29">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -7665,6 +7671,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576" xr:uid="{506D84C6-5465-4B2D-A9EA-2AFD69A75A90}">
+      <formula1>"OS Halfsets,OS Bangles / Bracelets"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -7673,19 +7684,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L71"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="2" max="3" width="21.1796875" customWidth="1"/>
+    <col min="4" max="4" width="24.7265625" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" customWidth="1"/>
     <col min="11" max="11" width="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.25">
+    <row r="1" spans="1:12" ht="17">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -9076,7 +9088,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -9110,7 +9122,7 @@
         <v>24</v>
       </c>
       <c r="L42" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -9144,7 +9156,7 @@
         <v>24</v>
       </c>
       <c r="L43" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -9178,7 +9190,7 @@
         <v>24</v>
       </c>
       <c r="L44" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -9212,7 +9224,7 @@
         <v>24</v>
       </c>
       <c r="L45" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -9246,7 +9258,7 @@
         <v>24</v>
       </c>
       <c r="L46" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -9280,7 +9292,7 @@
         <v>24</v>
       </c>
       <c r="L47" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -10100,23 +10112,28 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L1048576" xr:uid="{6903499B-E969-4EBF-9F67-B5114D71ED5D}">
+      <formula1>"Chains,PG Bangles / Bracelets"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Y40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.42578125" customWidth="1"/>
-    <col min="25" max="25" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.453125" customWidth="1"/>
+    <col min="25" max="25" width="24.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="35.25" thickBot="1">
+    <row r="1" spans="1:25" ht="34.5" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12609,25 +12626,30 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1:Y1048576" xr:uid="{126FE1E6-5B03-43AE-BF12-73EF9FFAC5CD}">
+      <formula1>"Vilandi Halfsets,Vilandi Bangles / Bracelets"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:X94"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" customWidth="1"/>
-    <col min="19" max="19" width="20.28515625" customWidth="1"/>
-    <col min="20" max="21" width="27.42578125" customWidth="1"/>
-    <col min="24" max="24" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="2" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="29.54296875" customWidth="1"/>
+    <col min="17" max="17" width="13.1796875" customWidth="1"/>
+    <col min="19" max="19" width="20.26953125" customWidth="1"/>
+    <col min="20" max="21" width="27.453125" customWidth="1"/>
+    <col min="24" max="24" width="24.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="51.75">
+    <row r="1" spans="1:24" ht="51">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -18108,6 +18130,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X1:X1048576" xr:uid="{AB63920D-B85F-436B-818A-D68C07A42189}">
+      <formula1>"Jadtar Register,Jadtar Halfsets,Jadtar Bangles / Bracelets,Only Earrings"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>